--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>sku</t>
   </si>
@@ -139,229 +139,25 @@
     <t>毛重</t>
   </si>
   <si>
-    <t>净重</t>
-  </si>
-  <si>
-    <t>箱规</t>
-  </si>
-  <si>
-    <t>单箱重量</t>
-  </si>
-  <si>
-    <t>单箱数量</t>
-  </si>
-  <si>
-    <t>ean码</t>
-  </si>
-  <si>
-    <t>计划首批下单量</t>
-  </si>
-  <si>
-    <t>首批下单时间</t>
-  </si>
-  <si>
-    <t>预计首批到货时间</t>
-  </si>
-  <si>
-    <t>MOQ(最小起订量)</t>
-  </si>
-  <si>
-    <t>交货周期(天)</t>
-  </si>
-  <si>
-    <t>实际首批到货时间</t>
-  </si>
-  <si>
-    <t>实际首批到货量</t>
-  </si>
-  <si>
-    <t>首批到货状态</t>
-  </si>
-  <si>
-    <t>采购员</t>
-  </si>
-  <si>
-    <t>一级供应商</t>
-  </si>
-  <si>
-    <t>二级供应商</t>
-  </si>
-  <si>
-    <t>错误信息</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.saleMethod}</t>
-  </si>
-  <si>
-    <t>{.productSellSpot}</t>
-  </si>
-  <si>
-    <t>{.productFunctionDesc}</t>
-  </si>
-  <si>
-    <t>{.usageDesc}</t>
-  </si>
-  <si>
-    <t>{.pirateRisk}</t>
-  </si>
-  <si>
-    <t>{.materials}</t>
-  </si>
-  <si>
-    <t>{.name}</t>
-  </si>
-  <si>
-    <t>{.brandName}</t>
-  </si>
-  <si>
-    <t>{.property}</t>
-  </si>
-  <si>
-    <t>{.planListingTime}</t>
-  </si>
-  <si>
-    <t>{.unitName}</t>
-  </si>
-  <si>
-    <t>{.chargeName}</t>
-  </si>
-  <si>
-    <t>{.targetTaxCost}</t>
-  </si>
-  <si>
-    <t>{.targetNoTaxCost}</t>
-  </si>
-  <si>
-    <t>{.actualTaxCost}</t>
-  </si>
-  <si>
-    <t>{.actualNoTaxCost}</t>
-  </si>
-  <si>
-    <t>{.retailPrice}</t>
-  </si>
-  <si>
-    <t>{.targetGpm}</t>
-  </si>
-  <si>
-    <t>{.actualGpmCny}</t>
-  </si>
-  <si>
-    <t>{.actualGpmUsd}</t>
-  </si>
-  <si>
-    <t>{.yearSaleQty}</t>
-  </si>
-  <si>
-    <t>{.yearSaleAmount}</t>
-  </si>
-  <si>
-    <t>{.monthSaleQty}</t>
-  </si>
-  <si>
-    <t>{.monthSaleAmount}</t>
-  </si>
-  <si>
-    <t>{.saleCountry}</t>
-  </si>
-  <si>
-    <t>{.listingTime}</t>
-  </si>
-  <si>
-    <t>{.delistingTime}</t>
-  </si>
-  <si>
-    <t>{.isFinishedImg}</t>
-  </si>
-  <si>
-    <t>{.isFinishedVideo}</t>
-  </si>
-  <si>
-    <t>{.saleState}</t>
-  </si>
-  <si>
-    <t>{.productProperty}</t>
-  </si>
-  <si>
-    <t>{.declareChineseName}</t>
-  </si>
-  <si>
-    <t>{.declareEnglishName}</t>
-  </si>
-  <si>
-    <t>{.declarePrice}</t>
-  </si>
-  <si>
-    <t>{.customsCode}</t>
-  </si>
-  <si>
-    <t>{.declareElement}</t>
-  </si>
-  <si>
-    <t>{.englishMaterial}</t>
-  </si>
-  <si>
-    <t>{.englishUsage}</t>
-  </si>
-  <si>
-    <t>{.productSize}</t>
-  </si>
-  <si>
-    <t>{.grossWeight}</t>
-  </si>
-  <si>
-    <t>{.netWeight}</t>
-  </si>
-  <si>
-    <t>{.boxSize}</t>
-  </si>
-  <si>
-    <t>{.boxWeight}</t>
-  </si>
-  <si>
-    <t>{.boxQty}</t>
-  </si>
-  <si>
-    <t>{.ean}</t>
-  </si>
-  <si>
-    <t>{.planOrderQty}</t>
-  </si>
-  <si>
-    <t>{.placeOrderTime}</t>
-  </si>
-  <si>
-    <t>{.planArrivalTime}</t>
-  </si>
-  <si>
-    <t>{.moq}</t>
-  </si>
-  <si>
-    <t>{.deliveryCycle}</t>
-  </si>
-  <si>
-    <t>{.actualArrivalTime}</t>
-  </si>
-  <si>
-    <t>{.actualArrivalQty}</t>
-  </si>
-  <si>
-    <t>{.arrivalState}</t>
-  </si>
-  <si>
-    <t>{.purchaseUser}</t>
-  </si>
-  <si>
-    <t>{.mainSupplier}</t>
-  </si>
-  <si>
-    <t>{.secondSupplier}</t>
-  </si>
-  <si>
-    <t>{.errorMsg}</t>
+    <t>月份</t>
+  </si>
+  <si>
+    <t>部门名称</t>
+  </si>
+  <si>
+    <t>平台名称</t>
+  </si>
+  <si>
+    <t>站点</t>
+  </si>
+  <si>
+    <t>店铺名称</t>
+  </si>
+  <si>
+    <t>负责人</t>
+  </si>
+  <si>
+    <t>组合</t>
   </si>
 </sst>
 </file>
@@ -375,7 +171,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -386,13 +182,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -869,48 +658,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -920,101 +712,98 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1025,9 +814,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1349,7 +1135,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BF6"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
@@ -1372,18 +1158,9 @@
     <col min="46" max="46" width="7.125" customWidth="1"/>
     <col min="47" max="47" width="13" customWidth="1"/>
     <col min="48" max="48" width="11.125" customWidth="1"/>
-    <col min="49" max="49" width="14.5" customWidth="1"/>
-    <col min="50" max="50" width="11.25" customWidth="1"/>
-    <col min="51" max="51" width="14.125" customWidth="1"/>
-    <col min="52" max="52" width="14.875" customWidth="1"/>
-    <col min="53" max="53" width="12.375" customWidth="1"/>
-    <col min="55" max="55" width="10.75" customWidth="1"/>
-    <col min="56" max="56" width="10.625" customWidth="1"/>
-    <col min="57" max="57" width="11.125" customWidth="1"/>
-    <col min="58" max="58" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:58">
+    <row r="1" customFormat="1" spans="1:48">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1528,212 +1305,56 @@
       <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" s="4" t="s">
-        <v>57</v>
-      </c>
     </row>
-    <row r="2" spans="1:58">
-      <c r="A2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>115</v>
-      </c>
+    <row r="2" spans="1:48">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="2"/>
     </row>
     <row r="5" spans="45:45">
       <c r="AS5" s="3"/>
@@ -1742,8 +1363,8 @@
       <c r="AS6" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="9">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AV2 AW2 AZ2">
+  <dataValidations count="7">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AV2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
@@ -1751,7 +1372,7 @@
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2 BA2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
@@ -1767,17 +1388,9 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
@@ -14,130 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
-  <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>销售方式</t>
-  </si>
-  <si>
-    <t>产品卖点</t>
-  </si>
-  <si>
-    <t>产品功能描述</t>
-  </si>
-  <si>
-    <t>产品用途</t>
-  </si>
-  <si>
-    <t>存在侵权风险</t>
-  </si>
-  <si>
-    <t>主要材质</t>
-  </si>
-  <si>
-    <t>品名</t>
-  </si>
-  <si>
-    <t>品牌</t>
-  </si>
-  <si>
-    <t>产品属性</t>
-  </si>
-  <si>
-    <t>计划上市时间</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>产品经理</t>
-  </si>
-  <si>
-    <t>目标含税成本</t>
-  </si>
-  <si>
-    <t>目标不含税成本</t>
-  </si>
-  <si>
-    <t>实际含税成本</t>
-  </si>
-  <si>
-    <t>实际不含税成本</t>
-  </si>
-  <si>
-    <t>标准零售价</t>
-  </si>
-  <si>
-    <t>目标毛利率</t>
-  </si>
-  <si>
-    <t>实际毛利率(人民币)</t>
-  </si>
-  <si>
-    <t>实际毛利率(美元)</t>
-  </si>
-  <si>
-    <t>年目标销售量</t>
-  </si>
-  <si>
-    <t>年目标销售额</t>
-  </si>
-  <si>
-    <t>月目标销售量</t>
-  </si>
-  <si>
-    <t>月目标销售额</t>
-  </si>
-  <si>
-    <t>销售国家</t>
-  </si>
-  <si>
-    <t>上市时间</t>
-  </si>
-  <si>
-    <t>退市时间</t>
-  </si>
-  <si>
-    <t>图片是否完成</t>
-  </si>
-  <si>
-    <t>视频是否完成</t>
-  </si>
-  <si>
-    <t>销售状态</t>
-  </si>
-  <si>
-    <t>报关产品属性</t>
-  </si>
-  <si>
-    <t>报关中文名</t>
-  </si>
-  <si>
-    <t>报关英文名</t>
-  </si>
-  <si>
-    <t>报关申报价格</t>
-  </si>
-  <si>
-    <t>海关编码</t>
-  </si>
-  <si>
-    <t>申报要素</t>
-  </si>
-  <si>
-    <t>英文材质</t>
-  </si>
-  <si>
-    <t>英文用途</t>
-  </si>
-  <si>
-    <t>产品尺寸</t>
-  </si>
-  <si>
-    <t>毛重</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>月份</t>
   </si>
@@ -1135,32 +1012,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AV6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="14" max="14" width="11.5" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="13.25" customWidth="1"/>
-    <col min="18" max="18" width="9.625" customWidth="1"/>
-    <col min="19" max="19" width="9.375" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="14.875" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="12.375" customWidth="1"/>
-    <col min="24" max="24" width="12.125" customWidth="1"/>
-    <col min="25" max="25" width="12.25" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="30" max="30" width="11.125" customWidth="1"/>
-    <col min="31" max="32" width="8.125" customWidth="1"/>
-    <col min="33" max="34" width="9.25" customWidth="1"/>
-    <col min="35" max="35" width="10.875" customWidth="1"/>
-    <col min="46" max="46" width="7.125" customWidth="1"/>
-    <col min="47" max="47" width="13" customWidth="1"/>
-    <col min="48" max="48" width="11.125" customWidth="1"/>
+    <col min="5" max="5" width="7.125" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:48">
+    <row r="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1182,215 +1042,43 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
     </row>
-    <row r="2" spans="1:48">
+    <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
-      <c r="AM2" s="1"/>
-      <c r="AN2" s="1"/>
-      <c r="AO2" s="1"/>
-      <c r="AP2" s="1"/>
-      <c r="AQ2" s="1"/>
-      <c r="AR2" s="1"/>
-      <c r="AS2" s="1"/>
-      <c r="AT2" s="1"/>
-      <c r="AU2" s="1"/>
-      <c r="AV2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
-    <row r="5" spans="45:45">
-      <c r="AS5" s="3"/>
+    <row r="5" spans="4:4">
+      <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="45:45">
-      <c r="AS6" s="3"/>
+    <row r="6" spans="4:4">
+      <c r="D6" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AV2">
-      <formula1>32874</formula1>
-      <formula2>2958101</formula2>
+  <dataValidations count="5">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:U2">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 Y2 AR2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2">
-      <formula1>0</formula1>
-      <formula2>9999999999999</formula2>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
+      <formula1>32874</formula1>
+      <formula2>2958101</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
@@ -680,11 +680,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1044,19 +1047,21 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1"/>
+      <c r="A2" s="2">
+        <v>43952</v>
+      </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="2"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="5" spans="4:4">
-      <c r="D5" s="3"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="4:4">
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="5">

--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
@@ -19,7 +19,7 @@
     <t>月份</t>
   </si>
   <si>
-    <t>部门名称</t>
+    <t>销售事业部</t>
   </si>
   <si>
     <t>平台名称</t>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>43952</v>
+        <v>45778</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1064,26 +1064,10 @@
       <c r="D6" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
-      <formula1>32874</formula1>
-      <formula2>2958101</formula2>
+  <dataValidations count="1">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>月份</t>
   </si>
@@ -35,6 +35,27 @@
   </si>
   <si>
     <t>组合</t>
+  </si>
+  <si>
+    <t>成本数据1</t>
+  </si>
+  <si>
+    <t>成本数据2</t>
+  </si>
+  <si>
+    <t>淘宝</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>天猫-优篮子旗舰店</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>淘宝有篮子</t>
   </si>
 </sst>
 </file>
@@ -48,8 +69,24 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="22">
-    <font>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
@@ -409,7 +446,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -427,9 +464,18 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color auto="1"/>
-      </bottom>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -535,165 +581,177 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="57" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1015,15 +1073,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="5" max="5" width="7.125" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="20.75" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="11.125" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:7">
+    <row r="1" customFormat="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1042,26 +1102,66 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2">
-        <v>45778</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="3"/>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4">
+        <v>44682</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2">
+        <v>26</v>
+      </c>
+      <c r="I2">
+        <v>36</v>
+      </c>
     </row>
     <row r="5" spans="4:4">
-      <c r="D5" s="4"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="4:4">
-      <c r="D6" s="4"/>
+      <c r="D6" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCost.xlsx
@@ -13,49 +13,82 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+例如：2022年5月</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+成本项，例如：销售成本</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>月份</t>
+    <t>*月份</t>
   </si>
   <si>
-    <t>销售事业部</t>
+    <t>*销售事业部</t>
   </si>
   <si>
-    <t>平台名称</t>
+    <t>*平台名称</t>
   </si>
   <si>
-    <t>站点</t>
+    <t>*站点</t>
   </si>
   <si>
-    <t>店铺名称</t>
+    <t>*店铺名称</t>
   </si>
   <si>
-    <t>负责人</t>
+    <t>*负责人</t>
   </si>
   <si>
     <t>组合</t>
-  </si>
-  <si>
-    <t>成本数据1</t>
-  </si>
-  <si>
-    <t>成本数据2</t>
-  </si>
-  <si>
-    <t>淘宝</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>天猫-优篮子旗舰店</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>淘宝有篮子</t>
   </si>
 </sst>
 </file>
@@ -69,7 +102,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -250,6 +283,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1105,12 +1149,8 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -1128,34 +1168,14 @@
       <c r="X1" s="8"/>
       <c r="Y1" s="8"/>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="4">
-        <v>44682</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2">
-        <v>26</v>
-      </c>
-      <c r="I2">
-        <v>36</v>
-      </c>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" s="7"/>
@@ -1172,5 +1192,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>